--- a/assets/data/ryuutama items.xlsx
+++ b/assets/data/ryuutama items.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\bizen\WebstormProjects\A-Quartermaster\src\assets\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EC07B61B-C24A-4D7E-8294-ECED29348E7E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{519A52AF-36D4-46EE-B706-B564CD39E15C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="19440" windowHeight="15600" tabRatio="500" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="19440" windowHeight="15600" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Items" sheetId="9" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="300" uniqueCount="274">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="297" uniqueCount="274">
   <si>
     <t>A type of melon that thrives in grottos of dried wood. From its leaves to its roots, even its fruit is well known for being jet black. It has the distinct odor of cheese. Really stinky cheese.</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -2495,8 +2495,8 @@
       <c r="D2">
         <v>1</v>
       </c>
-      <c r="E2" t="s">
-        <v>100</v>
+      <c r="E2">
+        <v>1</v>
       </c>
       <c r="F2" t="s">
         <v>76</v>
@@ -2512,8 +2512,8 @@
       <c r="D3">
         <v>1</v>
       </c>
-      <c r="E3" t="s">
-        <v>100</v>
+      <c r="E3">
+        <v>1</v>
       </c>
       <c r="F3" t="s">
         <v>77</v>
@@ -2563,8 +2563,8 @@
       <c r="D6">
         <v>3</v>
       </c>
-      <c r="E6" t="s">
-        <v>100</v>
+      <c r="E6">
+        <v>10</v>
       </c>
       <c r="F6" t="s">
         <v>46</v>
